--- a/expt/upstream_A.xlsx
+++ b/expt/upstream_A.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Processed" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Helpers" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -454,7 +455,7 @@
         <v/>
       </c>
       <c r="D2">
-        <f>'[upstream_B.xlsx]RawData'!B2*'[upstream_B.xlsx]FXRates'!B2</f>
+        <f>B2*Helpers!B2</f>
         <v/>
       </c>
     </row>
@@ -473,7 +474,7 @@
         <v/>
       </c>
       <c r="D3">
-        <f>'[upstream_B.xlsx]RawData'!B3*'[upstream_B.xlsx]FXRates'!B3</f>
+        <f>B3*Helpers!B3</f>
         <v/>
       </c>
     </row>
@@ -492,7 +493,7 @@
         <v/>
       </c>
       <c r="D4">
-        <f>'[upstream_B.xlsx]RawData'!B4*'[upstream_B.xlsx]FXRates'!B4</f>
+        <f>B4*Helpers!B4</f>
         <v/>
       </c>
     </row>
@@ -511,7 +512,7 @@
         <v/>
       </c>
       <c r="D5">
-        <f>'[upstream_B.xlsx]RawData'!B5*'[upstream_B.xlsx]FXRates'!B5</f>
+        <f>B5*Helpers!B5</f>
         <v/>
       </c>
     </row>
@@ -530,7 +531,7 @@
         <v/>
       </c>
       <c r="D6">
-        <f>'[upstream_B.xlsx]RawData'!B6*'[upstream_B.xlsx]FXRates'!B6</f>
+        <f>B6*Helpers!B6</f>
         <v/>
       </c>
     </row>
@@ -549,7 +550,7 @@
         <v/>
       </c>
       <c r="D7">
-        <f>'[upstream_B.xlsx]RawData'!B7*'[upstream_B.xlsx]FXRates'!B7</f>
+        <f>B7*Helpers!B7</f>
         <v/>
       </c>
     </row>
@@ -568,7 +569,7 @@
         <v/>
       </c>
       <c r="D8">
-        <f>'[upstream_B.xlsx]RawData'!B8*'[upstream_B.xlsx]FXRates'!B8</f>
+        <f>B8*Helpers!B8</f>
         <v/>
       </c>
     </row>
@@ -587,7 +588,7 @@
         <v/>
       </c>
       <c r="D9">
-        <f>'[upstream_B.xlsx]RawData'!B9*'[upstream_B.xlsx]FXRates'!B9</f>
+        <f>B9*Helpers!B9</f>
         <v/>
       </c>
     </row>
@@ -602,6 +603,157 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Adjusted FX</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Inflation Factor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Q1-2024</t>
+        </is>
+      </c>
+      <c r="B2">
+        <f>'[upstream_B.xlsx]FXRates'!B2*C2</f>
+        <v/>
+      </c>
+      <c r="C2">
+        <f>'[macro_data.xlsx]Inflation'!A2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Q2-2024</t>
+        </is>
+      </c>
+      <c r="B3">
+        <f>'[upstream_B.xlsx]FXRates'!B3*C3</f>
+        <v/>
+      </c>
+      <c r="C3">
+        <f>'[macro_data.xlsx]Inflation'!A3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Q3-2024</t>
+        </is>
+      </c>
+      <c r="B4">
+        <f>'[upstream_B.xlsx]FXRates'!B4*C4</f>
+        <v/>
+      </c>
+      <c r="C4">
+        <f>'[macro_data.xlsx]Inflation'!A4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Q4-2024</t>
+        </is>
+      </c>
+      <c r="B5">
+        <f>'[upstream_B.xlsx]FXRates'!B5*C5</f>
+        <v/>
+      </c>
+      <c r="C5">
+        <f>'[macro_data.xlsx]Inflation'!A5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Q1-2025</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>'[upstream_B.xlsx]FXRates'!B6*C6</f>
+        <v/>
+      </c>
+      <c r="C6">
+        <f>'[macro_data.xlsx]Inflation'!A6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Q2-2025</t>
+        </is>
+      </c>
+      <c r="B7">
+        <f>'[upstream_B.xlsx]FXRates'!B7*C7</f>
+        <v/>
+      </c>
+      <c r="C7">
+        <f>'[macro_data.xlsx]Inflation'!A7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Q3-2025</t>
+        </is>
+      </c>
+      <c r="B8">
+        <f>'[upstream_B.xlsx]FXRates'!B8*C8</f>
+        <v/>
+      </c>
+      <c r="C8">
+        <f>'[macro_data.xlsx]Inflation'!A8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Q4-2025</t>
+        </is>
+      </c>
+      <c r="B9">
+        <f>'[upstream_B.xlsx]FXRates'!B9*C9</f>
+        <v/>
+      </c>
+      <c r="C9">
+        <f>'[macro_data.xlsx]Inflation'!A9</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
